--- a/data/test_students.xlsx
+++ b/data/test_students.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="D2" t="n">
